--- a/dataset/review result/go_result_gpt-4-turbo-preview_2024-04-07 01_20_54.xlsx
+++ b/dataset/review result/go_result_gpt-4-turbo-preview_2024-04-07 01_20_54.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oywy2\Desktop\dataset\review result\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\LLM-CMT\dataset\review result\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38CA20E4-A570-4F07-8ABA-EDB86B126849}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71770C36-206C-4FA6-BBFD-448527517D90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-690" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28170" yWindow="-2220" windowWidth="20240" windowHeight="13260" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <calcPr calcId="0"/>
   <pivotCaches>
-    <pivotCache cacheId="1" r:id="rId3"/>
+    <pivotCache cacheId="0" r:id="rId3"/>
   </pivotCaches>
 </workbook>
 </file>
@@ -590,70 +590,71 @@
     <t>SHA-256 is used for hashing passwords without salting and stretching, making it susceptible to brute-force attacks due to its fast computation. For secure password storage, it is recommended to use algorithms designed for this purpose, such as Argon2, bcrypt, or scrypt, which incorporate salting and key stretching mechanisms.</t>
   </si>
   <si>
+    <t>120auth.go</t>
+  </si>
+  <si>
+    <t>Insecure PBE algorithm (PBKDF2 with SHA-1)</t>
+  </si>
+  <si>
+    <t>The use of PBKDF2 with SHA-1 as the hashing algorithm is considered insecure due to SHA-1's vulnerabilities to collision attacks. It's recommended to use a more secure hashing algorithm like SHA-256 or SHA-512.</t>
+  </si>
+  <si>
+    <t>D:\Users\oywy2\PycharmProjects\chatgptCMT\dataset\Go_code\23_1_12_go\data2\120chrome_unix.go</t>
+  </si>
+  <si>
+    <t>120chrome_unix.go</t>
+  </si>
+  <si>
+    <t>Insecure static IV for AES encryption</t>
+  </si>
+  <si>
+    <t>The use of a static, predictable initialization vector (IV) for AES encryption compromises the security of the encrypted data. IVs should be unpredictable and unique for each encryption operation.</t>
+  </si>
+  <si>
+    <t>Insufficient iteration count for PBKDF2</t>
+  </si>
+  <si>
+    <t>The iteration count for PBKDF2 is set to 1, which is insufficient for modern security standards. A higher iteration count, such as 10000 or more, is recommended to increase the computational effort required to derive keys.</t>
+  </si>
+  <si>
+    <t>D:\Users\oywy2\PycharmProjects\chatgptCMT\dataset\Go_code\23_1_12_go\data2\115server.go</t>
+  </si>
+  <si>
+    <t>115server.go</t>
+  </si>
+  <si>
+    <t>Weak password hashing mechanism</t>
+  </si>
+  <si>
+    <t>The code snippet from '115server.go' uses PBKDF2 with SHA-256 for password hashing, which is considered a secure choice. However, the iteration count is set to 600,000, which might not be sufficient depending on the application's threat model and the hardware capabilities of potential attackers. It's recommended to regularly review and adjust the iteration count based on current hardware performance trends and cryptographic recommendations.</t>
+  </si>
+  <si>
+    <t>D:\Users\oywy2\PycharmProjects\chatgptCMT\dataset\Go_code\23_1_12_go\data2\116utils_test.go</t>
+  </si>
+  <si>
+    <t>116utils_test.go</t>
+  </si>
+  <si>
+    <t>Use of SHA-256 for non-cryptographic purposes</t>
+  </si>
+  <si>
+    <t>The code snippet from '116utils_test.go' uses SHA-256 hashing in a testing context, which is not a misuse per se. However, it's important to note that SHA-256 is a cryptographic hash function, and its use should be limited to cryptographic applications. For non-cryptographic purposes, such as generating a hash for data integrity checks, non-cryptographic hash functions or checksums might be more appropriate and efficient.</t>
+  </si>
+  <si>
+    <t>行标签</t>
+  </si>
+  <si>
+    <t>(空白)</t>
+  </si>
+  <si>
+    <t>总计</t>
+  </si>
+  <si>
+    <t>Insecure PBE algorithm (PBKDF2 with SHA-1)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>D:\Users\oywy2\PycharmProjects\chatgptCMT\dataset\Go_code\23_1_12_go\data2\120auth.go</t>
-  </si>
-  <si>
-    <t>120auth.go</t>
-  </si>
-  <si>
-    <t>Insecure PBE algorithm (PBKDF2 with SHA-1)</t>
-  </si>
-  <si>
-    <t>The use of PBKDF2 with SHA-1 as the hashing algorithm is considered insecure due to SHA-1's vulnerabilities to collision attacks. It's recommended to use a more secure hashing algorithm like SHA-256 or SHA-512.</t>
-  </si>
-  <si>
-    <t>D:\Users\oywy2\PycharmProjects\chatgptCMT\dataset\Go_code\23_1_12_go\data2\120chrome_unix.go</t>
-  </si>
-  <si>
-    <t>120chrome_unix.go</t>
-  </si>
-  <si>
-    <t>Insecure static IV for AES encryption</t>
-  </si>
-  <si>
-    <t>The use of a static, predictable initialization vector (IV) for AES encryption compromises the security of the encrypted data. IVs should be unpredictable and unique for each encryption operation.</t>
-  </si>
-  <si>
-    <t>Insufficient iteration count for PBKDF2</t>
-  </si>
-  <si>
-    <t>The iteration count for PBKDF2 is set to 1, which is insufficient for modern security standards. A higher iteration count, such as 10000 or more, is recommended to increase the computational effort required to derive keys.</t>
-  </si>
-  <si>
-    <t>D:\Users\oywy2\PycharmProjects\chatgptCMT\dataset\Go_code\23_1_12_go\data2\115server.go</t>
-  </si>
-  <si>
-    <t>115server.go</t>
-  </si>
-  <si>
-    <t>Weak password hashing mechanism</t>
-  </si>
-  <si>
-    <t>The code snippet from '115server.go' uses PBKDF2 with SHA-256 for password hashing, which is considered a secure choice. However, the iteration count is set to 600,000, which might not be sufficient depending on the application's threat model and the hardware capabilities of potential attackers. It's recommended to regularly review and adjust the iteration count based on current hardware performance trends and cryptographic recommendations.</t>
-  </si>
-  <si>
-    <t>D:\Users\oywy2\PycharmProjects\chatgptCMT\dataset\Go_code\23_1_12_go\data2\116utils_test.go</t>
-  </si>
-  <si>
-    <t>116utils_test.go</t>
-  </si>
-  <si>
-    <t>Use of SHA-256 for non-cryptographic purposes</t>
-  </si>
-  <si>
-    <t>The code snippet from '116utils_test.go' uses SHA-256 hashing in a testing context, which is not a misuse per se. However, it's important to note that SHA-256 is a cryptographic hash function, and its use should be limited to cryptographic applications. For non-cryptographic purposes, such as generating a hash for data integrity checks, non-cryptographic hash functions or checksums might be more appropriate and efficient.</t>
-  </si>
-  <si>
-    <t>行标签</t>
-  </si>
-  <si>
-    <t>(空白)</t>
-  </si>
-  <si>
-    <t>总计</t>
-  </si>
-  <si>
-    <t>Insecure PBE algorithm (PBKDF2 with SHA-1)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -664,7 +665,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="yyyy/m/d\ h:mm:ss"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -681,12 +682,18 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -708,13 +715,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -998,7 +1007,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0B0302BA-9022-4F5A-870D-4F33677F1F26}" name="数据透视表1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0B0302BA-9022-4F5A-870D-4F33677F1F26}" name="数据透视表1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:A52" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="1">
     <pivotField axis="axisRow" showAll="0">
@@ -1520,259 +1529,259 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4B9DC6C-7CBE-46E1-A84B-284956AF1F42}">
   <dimension ref="A3:A52"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="32.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:1">
       <c r="A3" s="2" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
       <c r="A4" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:1">
       <c r="A5" s="3" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
       <c r="A6" s="3" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
       <c r="A7" s="3" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
       <c r="A8" s="3" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
       <c r="A9" s="3" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:1">
       <c r="A10" s="3" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:1">
       <c r="A11" s="3" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:1">
       <c r="A12" s="3" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:1">
       <c r="A13" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:1">
       <c r="A14" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:1">
       <c r="A15" s="3" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:1">
       <c r="A16" s="3" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:1">
       <c r="A17" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:1">
       <c r="A18" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:1">
       <c r="A19" s="3" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:1">
       <c r="A20" s="3" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:1">
       <c r="A21" s="3" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:1">
       <c r="A22" s="3" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:1">
       <c r="A23" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:1">
       <c r="A24" s="3" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:1">
       <c r="A25" s="3" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:1">
       <c r="A26" s="3" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:1">
       <c r="A27" s="3" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:1">
       <c r="A28" s="3" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:1">
       <c r="A29" s="3" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:1">
       <c r="A30" s="3" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:1">
       <c r="A31" s="3" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:1">
       <c r="A32" s="3" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:1">
       <c r="A33" s="3" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:1">
       <c r="A34" s="3" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:1">
       <c r="A35" s="3" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:1">
       <c r="A36" s="3" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:1">
       <c r="A37" s="3" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:1">
       <c r="A38" s="3" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:1">
       <c r="A39" s="3" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:1">
       <c r="A40" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:1">
       <c r="A41" s="3" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:1">
       <c r="A42" s="3" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:1">
       <c r="A43" s="3" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:1">
       <c r="A44" s="3" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:1">
       <c r="A45" s="3" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:1">
       <c r="A46" s="3" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:1">
       <c r="A47" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:1">
       <c r="A48" s="3" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:1">
       <c r="A49" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:1">
       <c r="A50" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:1">
       <c r="A51" s="3" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" s="3" t="s">
         <v>207</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A52" s="3" t="s">
-        <v>208</v>
       </c>
     </row>
   </sheetData>
@@ -1784,12 +1793,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M64"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="6" max="6" width="50.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1830,7 +1839,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -1865,7 +1874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -1900,7 +1909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -1935,7 +1944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -1970,7 +1979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -2008,7 +2017,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13">
       <c r="A7" t="s">
         <v>28</v>
       </c>
@@ -2043,7 +2052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -2078,7 +2087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13">
       <c r="A9" t="s">
         <v>34</v>
       </c>
@@ -2116,7 +2125,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13">
       <c r="A10" t="s">
         <v>38</v>
       </c>
@@ -2151,7 +2160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13">
       <c r="A11" t="s">
         <v>42</v>
       </c>
@@ -2186,7 +2195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13">
       <c r="A12" t="s">
         <v>46</v>
       </c>
@@ -2221,7 +2230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13">
       <c r="A13" t="s">
         <v>46</v>
       </c>
@@ -2256,7 +2265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13">
       <c r="A14" t="s">
         <v>42</v>
       </c>
@@ -2291,7 +2300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:13">
       <c r="A15" t="s">
         <v>46</v>
       </c>
@@ -2326,7 +2335,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13">
       <c r="A16" t="s">
         <v>56</v>
       </c>
@@ -2361,7 +2370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:13">
       <c r="A17" t="s">
         <v>60</v>
       </c>
@@ -2396,7 +2405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:13">
       <c r="A18" t="s">
         <v>62</v>
       </c>
@@ -2431,7 +2440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:13">
       <c r="A19" t="s">
         <v>64</v>
       </c>
@@ -2466,7 +2475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:13">
       <c r="A20" t="s">
         <v>66</v>
       </c>
@@ -2501,7 +2510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:13">
       <c r="A21" t="s">
         <v>66</v>
       </c>
@@ -2539,7 +2548,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:13">
       <c r="A22" t="s">
         <v>70</v>
       </c>
@@ -2577,7 +2586,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:13">
       <c r="A23" t="s">
         <v>74</v>
       </c>
@@ -2615,7 +2624,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:13">
       <c r="A24" t="s">
         <v>76</v>
       </c>
@@ -2650,7 +2659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:13">
       <c r="A25" t="s">
         <v>80</v>
       </c>
@@ -2685,7 +2694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:13">
       <c r="A26" t="s">
         <v>76</v>
       </c>
@@ -2723,7 +2732,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:13">
       <c r="A27" t="s">
         <v>84</v>
       </c>
@@ -2761,7 +2770,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:13">
       <c r="A28" t="s">
         <v>86</v>
       </c>
@@ -2796,7 +2805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:13">
       <c r="A29" t="s">
         <v>90</v>
       </c>
@@ -2831,7 +2840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:13">
       <c r="A30" t="s">
         <v>94</v>
       </c>
@@ -2869,7 +2878,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:13">
       <c r="A31" t="s">
         <v>98</v>
       </c>
@@ -2907,7 +2916,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:13">
       <c r="A32" t="s">
         <v>100</v>
       </c>
@@ -2945,7 +2954,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:13">
       <c r="A33" t="s">
         <v>102</v>
       </c>
@@ -2961,7 +2970,7 @@
       <c r="E33">
         <v>2165</v>
       </c>
-      <c r="F33" t="s">
+      <c r="F33" s="5" t="s">
         <v>104</v>
       </c>
       <c r="G33" t="s">
@@ -2979,11 +2988,11 @@
       <c r="K33">
         <v>1</v>
       </c>
-      <c r="M33" t="s">
+      <c r="M33" s="5" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:13">
       <c r="A34" t="s">
         <v>107</v>
       </c>
@@ -3018,7 +3027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:13">
       <c r="A35" t="s">
         <v>107</v>
       </c>
@@ -3056,7 +3065,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:13">
       <c r="A36" t="s">
         <v>107</v>
       </c>
@@ -3091,7 +3100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:13">
       <c r="A37" t="s">
         <v>114</v>
       </c>
@@ -3129,7 +3138,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:13">
       <c r="A38" t="s">
         <v>114</v>
       </c>
@@ -3164,7 +3173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:13">
       <c r="A39" t="s">
         <v>120</v>
       </c>
@@ -3202,7 +3211,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:13">
       <c r="A40" t="s">
         <v>124</v>
       </c>
@@ -3237,7 +3246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:13">
       <c r="A41" t="s">
         <v>128</v>
       </c>
@@ -3275,7 +3284,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:13">
       <c r="A42" t="s">
         <v>132</v>
       </c>
@@ -3313,7 +3322,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:13">
       <c r="A43" t="s">
         <v>136</v>
       </c>
@@ -3351,7 +3360,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:13">
       <c r="A44" t="s">
         <v>136</v>
       </c>
@@ -3389,7 +3398,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:13">
       <c r="A45" t="s">
         <v>136</v>
       </c>
@@ -3424,7 +3433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:13">
       <c r="A46" t="s">
         <v>144</v>
       </c>
@@ -3462,7 +3471,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:13">
       <c r="A47" t="s">
         <v>148</v>
       </c>
@@ -3500,7 +3509,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:13">
       <c r="A48" t="s">
         <v>152</v>
       </c>
@@ -3535,7 +3544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:13">
       <c r="A49" t="s">
         <v>156</v>
       </c>
@@ -3570,7 +3579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:13">
       <c r="A50" t="s">
         <v>160</v>
       </c>
@@ -3605,7 +3614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:13">
       <c r="A51" t="s">
         <v>160</v>
       </c>
@@ -3640,7 +3649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:13">
       <c r="A52" t="s">
         <v>160</v>
       </c>
@@ -3678,7 +3687,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:13">
       <c r="A53" t="s">
         <v>160</v>
       </c>
@@ -3716,7 +3725,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:13">
       <c r="A54" t="s">
         <v>170</v>
       </c>
@@ -3751,7 +3760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:13">
       <c r="A55" t="s">
         <v>170</v>
       </c>
@@ -3786,7 +3795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:13">
       <c r="A56" t="s">
         <v>176</v>
       </c>
@@ -3821,7 +3830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:13">
       <c r="A57" t="s">
         <v>180</v>
       </c>
@@ -3856,7 +3865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:13">
       <c r="A58" t="s">
         <v>184</v>
       </c>
@@ -3891,12 +3900,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A59" t="s">
+    <row r="59" spans="1:13">
+      <c r="A59" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="B59" t="s">
         <v>188</v>
-      </c>
-      <c r="B59" t="s">
-        <v>189</v>
       </c>
       <c r="C59">
         <v>-1</v>
@@ -3908,33 +3917,33 @@
         <v>2190</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G59" t="s">
+        <v>190</v>
+      </c>
+      <c r="H59" t="s">
+        <v>18</v>
+      </c>
+      <c r="I59" s="1">
+        <v>45389.056180555555</v>
+      </c>
+      <c r="J59">
+        <v>0</v>
+      </c>
+      <c r="K59">
+        <v>1</v>
+      </c>
+      <c r="L59" s="5" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13">
+      <c r="A60" t="s">
         <v>191</v>
       </c>
-      <c r="H59" t="s">
-        <v>18</v>
-      </c>
-      <c r="I59" s="1">
-        <v>45389.056180555555</v>
-      </c>
-      <c r="J59">
-        <v>0</v>
-      </c>
-      <c r="K59">
-        <v>1</v>
-      </c>
-      <c r="L59" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A60" t="s">
+      <c r="B60" t="s">
         <v>192</v>
-      </c>
-      <c r="B60" t="s">
-        <v>193</v>
       </c>
       <c r="C60">
         <v>-1</v>
@@ -3946,30 +3955,30 @@
         <v>2190</v>
       </c>
       <c r="F60" t="s">
+        <v>189</v>
+      </c>
+      <c r="G60" t="s">
         <v>190</v>
       </c>
-      <c r="G60" t="s">
+      <c r="H60" t="s">
+        <v>18</v>
+      </c>
+      <c r="I60" s="1">
+        <v>45389.056180555555</v>
+      </c>
+      <c r="J60">
+        <v>1</v>
+      </c>
+      <c r="K60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13">
+      <c r="A61" t="s">
         <v>191</v>
       </c>
-      <c r="H60" t="s">
-        <v>18</v>
-      </c>
-      <c r="I60" s="1">
-        <v>45389.056180555555</v>
-      </c>
-      <c r="J60">
-        <v>1</v>
-      </c>
-      <c r="K60">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A61" t="s">
+      <c r="B61" t="s">
         <v>192</v>
-      </c>
-      <c r="B61" t="s">
-        <v>193</v>
       </c>
       <c r="C61">
         <v>-1</v>
@@ -3981,11 +3990,11 @@
         <v>2191</v>
       </c>
       <c r="F61" t="s">
+        <v>193</v>
+      </c>
+      <c r="G61" t="s">
         <v>194</v>
       </c>
-      <c r="G61" t="s">
-        <v>195</v>
-      </c>
       <c r="H61" t="s">
         <v>18</v>
       </c>
@@ -3999,12 +4008,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:13">
       <c r="A62" t="s">
+        <v>191</v>
+      </c>
+      <c r="B62" t="s">
         <v>192</v>
-      </c>
-      <c r="B62" t="s">
-        <v>193</v>
       </c>
       <c r="C62">
         <v>-1</v>
@@ -4016,30 +4025,30 @@
         <v>2192</v>
       </c>
       <c r="F62" t="s">
+        <v>195</v>
+      </c>
+      <c r="G62" t="s">
         <v>196</v>
       </c>
-      <c r="G62" t="s">
+      <c r="H62" t="s">
+        <v>18</v>
+      </c>
+      <c r="I62" s="1">
+        <v>45389.056180555555</v>
+      </c>
+      <c r="J62">
+        <v>1</v>
+      </c>
+      <c r="K62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13">
+      <c r="A63" t="s">
         <v>197</v>
       </c>
-      <c r="H62" t="s">
-        <v>18</v>
-      </c>
-      <c r="I62" s="1">
-        <v>45389.056180555555</v>
-      </c>
-      <c r="J62">
-        <v>1</v>
-      </c>
-      <c r="K62">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A63" t="s">
+      <c r="B63" t="s">
         <v>198</v>
-      </c>
-      <c r="B63" t="s">
-        <v>199</v>
       </c>
       <c r="C63">
         <v>-1</v>
@@ -4051,30 +4060,30 @@
         <v>2193</v>
       </c>
       <c r="F63" t="s">
+        <v>199</v>
+      </c>
+      <c r="G63" t="s">
         <v>200</v>
       </c>
-      <c r="G63" t="s">
+      <c r="H63" t="s">
+        <v>18</v>
+      </c>
+      <c r="I63" s="1">
+        <v>45389.056180555555</v>
+      </c>
+      <c r="J63">
+        <v>1</v>
+      </c>
+      <c r="K63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13">
+      <c r="A64" t="s">
         <v>201</v>
       </c>
-      <c r="H63" t="s">
-        <v>18</v>
-      </c>
-      <c r="I63" s="1">
-        <v>45389.056180555555</v>
-      </c>
-      <c r="J63">
-        <v>1</v>
-      </c>
-      <c r="K63">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A64" t="s">
+      <c r="B64" t="s">
         <v>202</v>
-      </c>
-      <c r="B64" t="s">
-        <v>203</v>
       </c>
       <c r="C64">
         <v>-1</v>
@@ -4086,10 +4095,10 @@
         <v>2194</v>
       </c>
       <c r="F64" t="s">
+        <v>203</v>
+      </c>
+      <c r="G64" t="s">
         <v>204</v>
-      </c>
-      <c r="G64" t="s">
-        <v>205</v>
       </c>
       <c r="H64" t="s">
         <v>18</v>
